--- a/backend/reports/backend-report.xlsx
+++ b/backend/reports/backend-report.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8109</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8135</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8176</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8157</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8144</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8163</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8158</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1965</v>
+        <v>1549</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.88</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="8">
@@ -729,7 +729,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04T18:18:49.090135+00:00</t>
+          <t>2026-09-04T18:22:18.143195+00:00</t>
         </is>
       </c>
     </row>
